--- a/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_27-10-26.xlsx
+++ b/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_27-10-26.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27 Oct 2026 08:03 AM</t>
+          <t>27 Oct 2026 10:01 AM</t>
         </is>
       </c>
     </row>
